--- a/artfynd/A 45420-2022 artfynd.xlsx
+++ b/artfynd/A 45420-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45420-2022 artfynd.xlsx
+++ b/artfynd/A 45420-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110259646</v>
+        <v>120724560</v>
       </c>
       <c r="B2" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Näteselet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551384.4851022225</v>
+        <v>551409</v>
       </c>
       <c r="R2" t="n">
-        <v>6965079.652148084</v>
+        <v>6965204</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120724564</v>
+        <v>120724563</v>
       </c>
       <c r="B3" t="n">
-        <v>90453</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551402</v>
+        <v>551413</v>
       </c>
       <c r="R3" t="n">
-        <v>6965047</v>
+        <v>6965057</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120724545</v>
+        <v>120724564</v>
       </c>
       <c r="B4" t="n">
-        <v>57501</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551395</v>
+        <v>551402</v>
       </c>
       <c r="R4" t="n">
-        <v>6965137</v>
+        <v>6965047</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120724563</v>
+        <v>128633177</v>
       </c>
       <c r="B5" t="n">
-        <v>90453</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551413</v>
+        <v>551314</v>
       </c>
       <c r="R5" t="n">
-        <v>6965057</v>
+        <v>6965181</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,50 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120724547</v>
+        <v>97364696</v>
       </c>
       <c r="B6" t="n">
-        <v>91615</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Näteselet, Jmt</t>
+          <t>Skravelforsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551401</v>
+        <v>551276</v>
       </c>
       <c r="R6" t="n">
-        <v>6965047</v>
+        <v>6965112</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,49 +1148,48 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120724562</v>
+        <v>120724592</v>
       </c>
       <c r="B7" t="n">
-        <v>90453</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3215</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551419</v>
+        <v>551314</v>
       </c>
       <c r="R7" t="n">
-        <v>6965074</v>
+        <v>6965181</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,15 +1261,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120724560</v>
+        <v>120724547</v>
       </c>
       <c r="B8" t="n">
-        <v>90453</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,21 +1272,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551409</v>
+        <v>551401</v>
       </c>
       <c r="R8" t="n">
-        <v>6965204</v>
+        <v>6965047</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,6 +1355,297 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>110259646</v>
+      </c>
+      <c r="B9" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Getingfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>551384</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6965079</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120724545</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Näteselet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>551395</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6965137</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120724562</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91680</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Näteselet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>551419</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6965074</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45420-2022 artfynd.xlsx
+++ b/artfynd/A 45420-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97364696</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724560</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724562</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724563</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724564</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128633177</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724592</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724547</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110259646</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,8 +1696,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724545</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>